--- a/output/pdf_financials_xlsx/WRLG.xlsx
+++ b/output/pdf_financials_xlsx/WRLG.xlsx
@@ -6401,28 +6401,28 @@
         <v>0.094427</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.198059</v>
+        <v>0.24164</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.198059</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -6436,19 +6436,19 @@
         </is>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.198059</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.810651</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>19.089</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>26.623</v>
       </c>
     </row>
     <row r="93">
@@ -8011,10 +8011,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.020112</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0</v>
@@ -11346,7 +11346,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -15068,7 +15072,11 @@
           <t>Reserves 6,810,651</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -17250,7 +17258,11 @@
           <t>Reserves 198,059</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -20968,7 +20980,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -23170,7 +23186,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -39202,7 +39222,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WRLG.xlsx
+++ b/output/pdf_financials_xlsx/WRLG.xlsx
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001038</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.051025</v>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.011599</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.035537</v>
@@ -2176,10 +2176,10 @@
         <v>-0.512491</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.182065</v>
+        <v>-0.183103</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.153007</v>
+        <v>-0.204032</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.177279</v>
+        <v>-0.188878</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.227846</v>
@@ -2302,10 +2302,10 @@
         <v>-0.512491</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.182065</v>
+        <v>-0.183103</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.153007</v>
+        <v>-0.204032</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.177279</v>
+        <v>-0.188878</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.227846</v>
@@ -2575,40 +2575,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.245082</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.194522</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.1521</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.322635</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.210054</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.346261</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.174407</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.137641</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.061895</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.004212</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.552577</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.422927</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.017332</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.64123</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>16.308858</v>
@@ -2701,40 +2701,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.655788</v>
+        <v>0.9008699999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.194522</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.1521</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.322635</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.210054</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.346261</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.174407</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.137641</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.061895</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.004212</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.552577</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.422927</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.017332</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.64123</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>16.308858</v>
@@ -3457,40 +3457,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.247582</v>
+        <v>0.0025</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.197022</v>
+        <v>0.0025</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.9194020000000001</v>
+        <v>0.767302</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.322636</v>
+        <v>1e-06</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.344776</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.174407</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.137641</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.06083</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.00313</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.552577</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.422927</v>
+        <v>0</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -57604,7 +57604,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">

--- a/output/pdf_financials_xlsx/WRLG.xlsx
+++ b/output/pdf_financials_xlsx/WRLG.xlsx
@@ -8532,10 +8532,10 @@
         <v>0</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>-0.750008</v>
+        <v>-1.785019</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>-0.285003</v>
+        <v>-0.570006</v>
       </c>
       <c r="I126" s="3" t="n">
         <v>-0.285003</v>

--- a/output/pdf_financials_xlsx/WRLG.xlsx
+++ b/output/pdf_financials_xlsx/WRLG.xlsx
@@ -770,22 +770,22 @@
         <v>0.079625</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.045334</v>
+        <v>0.0401</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>0.02414</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.001127</v>
@@ -808,13 +808,13 @@
         <v>0.056254</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.02923</v>
+        <v>0.19023</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>3.125255</v>
+        <v>4.597368</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>5.667083</v>
+        <v>12.227967</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>0</v>
@@ -4966,13 +4966,13 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.288209</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>6.138</v>
       </c>
     </row>
     <row r="71">
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.288209</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>18.913</v>
+        <v>20.313</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>44.2</v>
+        <v>50.338</v>
       </c>
     </row>
     <row r="72">
@@ -5281,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>7.803257</v>
+        <v>7.515048</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5639,16 +5639,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q80" s="3" t="n">
+        <v>0.004364527920930429</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.6419237687947595</v>
+        <v>0.6894409937888198</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>0.4552758435993572</v>
+        <v>0.5184994437806436</v>
       </c>
     </row>
     <row r="81">
@@ -6940,10 +6938,10 @@
         <v>0.001385</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003559</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.004174</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>-0.000194</v>
@@ -7536,13 +7534,13 @@
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.262852</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.661</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>3.054</v>
       </c>
     </row>
     <row r="111">
@@ -7599,7 +7597,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.190847</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -9142,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.190847</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -9227,7 +9225,7 @@
         </is>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-26.145558</v>
+        <v>-26.336405</v>
       </c>
       <c r="R135" s="3" t="n">
         <v>-80.601888</v>
@@ -10628,7 +10626,11 @@
           <t>Lease liabilities (Note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -12482,7 +12484,11 @@
           <t>Lease liabilities (Note 6)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -14536,7 +14542,11 @@
           <t>Lease liabilities (Note 6) 288,209</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -27106,7 +27116,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -27844,7 +27858,11 @@
           <t>Reclamation accretion expense (Note 12)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -27948,7 +27966,11 @@
           <t>Credit facility accretion expense (Note 11)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -31818,7 +31840,11 @@
           <t>Reclamation accretion expense (Note 11)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -34564,7 +34590,11 @@
           <t>Reclamation accretion expense</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -35204,7 +35234,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -38930,7 +38964,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -40704,7 +40742,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -44702,7 +44744,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -46058,7 +46104,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E350" s="5" t="n">
         <v>0.341353</v>
       </c>
@@ -51044,7 +51094,11 @@
           <t>Salaries, benefits and directors’ fees (Note 13)</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
@@ -54774,7 +54828,11 @@
           <t>Salaries, benefits and directors’ fees $</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -56348,7 +56406,11 @@
           <t>Salaries, benefits and directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -61140,7 +61202,11 @@
           <t>Management and directors’ fees (Note 6)</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
@@ -63342,7 +63408,11 @@
           <t>Management and directors’ fees (Note 7)</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -64076,7 +64146,11 @@
           <t>Income taxes (recovery) (note 12)</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E522" t="inlineStr">
         <is>
           <t>-</t>
@@ -65960,7 +66034,11 @@
           <t>Income taxes - recovery (note 13)</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
